--- a/DRIVE MASTER NIRANTARA PLK UNY 2027/01_KESEKRETARIATAN/Master_Database_Profil_dan_K3_Tim.xlsx
+++ b/DRIVE MASTER NIRANTARA PLK UNY 2027/01_KESEKRETARIATAN/Master_Database_Profil_dan_K3_Tim.xlsx
@@ -478,20 +478,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,45 +523,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>NIM</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Panggilan</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Jenis Kelamin</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Prodi</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Fakultas</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Peran Operasional Posko</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Peran Divisi Proker</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>No. WhatsApp</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Alamat Domisili Jogja</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Daerah Asal</t>
         </is>
@@ -577,45 +583,50 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>24050530030</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>Fajar</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Laki-laki</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Pendidikan Teknik Informatika</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Ketua (Kordes)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Supervisi, Lobi Desa &amp; IT</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Kota Yogyakarta</t>
+          <t>0895-3638-98438</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Jl. Balapan 44, Klitren</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Yogyakarta</t>
         </is>
@@ -632,45 +643,50 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>24050530052</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>Terry</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Laki-laki</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Pendidikan Teknik Informatika</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Humas &amp; Tuan Rumah Posko</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Web Desa &amp; IT</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0857-7367-5282</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>PP Klaten</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Klaten</t>
         </is>
@@ -687,45 +703,50 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>24050530029</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>Riski</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Laki-laki</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Pendidikan Teknik Informatika</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Perlengkapan 1 (Logistik/Armada)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Web Desa &amp; IT</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0815-6636-087</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Jetis</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Bekasi</t>
         </is>
@@ -742,45 +763,50 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>24050530045</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>Veli</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Perempuan</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Pendidikan Teknik Informatika</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Sekretaris 2 (Logbook 272)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Koor. Divisi Teknologi &amp; IT</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0896-3618-6564</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Jl. Arumdalu no. 11</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Ponorogo</t>
         </is>
@@ -797,45 +823,50 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>24080330053</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>Dinda</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Perempuan</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Pendidikan Administrasi Perkantoran</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Sekretaris 1 (Proposal/LPJ)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Divisi Administrasi &amp; UMKM</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0813-2878-8545</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Samirono CT VI/306, Depok</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Klaten</t>
         </is>
@@ -852,45 +883,50 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>24080330078</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>Fay</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Perempuan</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Pendidikan Administrasi Perkantoran</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Bendahara 1 (Kas Utama/RAB)</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Koor. Divisi Administrasi &amp; UMKM</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0895-3359-78835</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Jl. Amarta I, Karang Malang</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Sukoharjo</t>
         </is>
@@ -907,45 +943,50 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>24030830059</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>Intan</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Perempuan</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Biologi</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>FMIPA</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>PDD 2 (Dokumentasi/Jurnalistik)</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Koor. Divisi Lingkungan &amp; Kesehatan</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0852-1786-6452</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Jl. Kwasen, Piyungan, Bantul</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Klaten</t>
         </is>
@@ -962,45 +1003,50 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>24030830068</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>Zalfa</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Perempuan</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Biologi</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>FMIPA</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Bendahara 2 (SPJ/Belanja Posko)</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Divisi Lingkungan &amp; Pupuk</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0838-8626-748</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Karangmalang, Blok C.19A</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Kuningan, Jabar</t>
         </is>
@@ -1017,45 +1063,50 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>24010530018</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>Vina</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Perempuan</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Teknologi Pendidikan</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>FIP</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>PDD 1 (Desain/Branding/Medsos)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Koor. Divisi Pendidikan &amp; Media Ajar</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0895-2882-4030</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Tirtomartani, Kalasan, Sleman</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Ceper, Klaten</t>
         </is>
@@ -1072,45 +1123,50 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>24010530004</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>Sandra</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Perempuan</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Teknologi Pendidikan</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>FIP</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Perlengkapan 2 (Operasional Acara)</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Divisi Pendidikan &amp; Media Ajar</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>08xxxxxxxxxx</t>
-        </is>
-      </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Yogyakarta</t>
+          <t>0812-1508-2869</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Gang Surya No.6, Santren</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Medan, Sumut</t>
         </is>
@@ -1132,11 +1188,11 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1168,27 +1224,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>NIM</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Golongan Darah</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Riwayat Alergi (Makanan/Obat)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Riwayat Sakit Khusus</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Nama Kontak Darurat (Ortu/Wali)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Hubungan</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1208,22 +1264,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
+          <t>24050530030</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Tidak ada</t>
+          <t>Eksim, dermatitis</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bronkitis, GERD</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1233,7 +1289,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0813-2657-5753</t>
         </is>
       </c>
     </row>
@@ -1248,22 +1304,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+          <t>24050530052</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sehat sentosa</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1273,7 +1329,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0815-1108-5683</t>
         </is>
       </c>
     </row>
@@ -1288,22 +1344,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+          <t>24050530029</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sehat sentosa</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1313,7 +1369,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1328,32 +1384,32 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+          <t>24050530045</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>AB+</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Suhu drastis, Lactose Intolerant</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Orang Tua</t>
+          <t>Bapak (Olief)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0896-3618-6564</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1424,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+          <t>24080330053</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gastritis &amp; GERD</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1393,7 +1449,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0838-4834-3763</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1464,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+          <t>24080330078</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sehat</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1433,7 +1489,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0812-2824-0759</t>
         </is>
       </c>
     </row>
@@ -1448,22 +1504,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+          <t>24030830059</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Asam Lambung (GERD)</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1473,7 +1529,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0857-1618-2143</t>
         </is>
       </c>
     </row>
@@ -1488,22 +1544,22 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
+          <t>24030830068</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Tidak ada</t>
+          <t>Dingin</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Maag</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1513,7 +1569,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0858-4647-6055</t>
         </is>
       </c>
     </row>
@@ -1528,32 +1584,32 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+          <t>24010530018</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sehat sentosa</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Orang Tua</t>
+          <t>Ibu</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0857-2514-7579</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1624,32 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+          <t>24010530004</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Tidak ada</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Tidak ada</t>
-        </is>
-      </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sehat sentosa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Orang Tua</t>
+          <t>Ibu</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>08xxxxxxxxxx</t>
+          <t>0813-9701-3302</t>
         </is>
       </c>
     </row>
